--- a/excel/map.xlsx
+++ b/excel/map.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>编号</t>
   </si>
@@ -92,6 +92,9 @@
     <t>boss索引</t>
   </si>
   <si>
+    <t>游戏人数</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -111,6 +114,9 @@
   </si>
   <si>
     <t>bossId</t>
+  </si>
+  <si>
+    <t>gameNumber</t>
   </si>
   <si>
     <t>int</t>
@@ -345,12 +351,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1193,51 +1199,60 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
@@ -1251,18 +1266,20 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3">
+        <v>4</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -1280,18 +1297,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <v>4</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -1309,18 +1328,20 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>5</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1338,18 +1359,20 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G7" s="3">
         <v>3</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>6</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1367,18 +1390,20 @@
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" s="3">
         <v>4</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>6</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1396,18 +1421,20 @@
         <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G9" s="3">
         <v>5</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>7</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -1425,18 +1452,20 @@
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G10" s="3">
         <v>6</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>6</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -1454,18 +1483,20 @@
         <v>2</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" s="3">
         <v>7</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3">
+        <v>7</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>

--- a/excel/map.xlsx
+++ b/excel/map.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>编号</t>
   </si>
@@ -95,6 +95,9 @@
     <t>游戏人数</t>
   </si>
   <si>
+    <t>游戏时长</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>gameNumber</t>
+  </si>
+  <si>
+    <t>gameTime</t>
   </si>
   <si>
     <t>int</t>
@@ -1202,57 +1208,66 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
@@ -1266,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -1280,7 +1295,9 @@
       <c r="H4" s="3">
         <v>4</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3">
+        <v>600</v>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -1297,13 +1314,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -1311,7 +1328,9 @@
       <c r="H5" s="3">
         <v>4</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="3">
+        <v>600</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -1328,13 +1347,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -1342,7 +1361,9 @@
       <c r="H6" s="3">
         <v>5</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="3">
+        <v>660</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -1359,13 +1380,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7" s="3">
         <v>3</v>
@@ -1373,7 +1394,9 @@
       <c r="H7" s="3">
         <v>6</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="3">
+        <v>720</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -1390,13 +1413,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8" s="3">
         <v>4</v>
@@ -1404,7 +1427,9 @@
       <c r="H8" s="3">
         <v>6</v>
       </c>
-      <c r="I8" s="3"/>
+      <c r="I8" s="3">
+        <v>720</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1421,13 +1446,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G9" s="3">
         <v>5</v>
@@ -1435,7 +1460,9 @@
       <c r="H9" s="3">
         <v>7</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="3">
+        <v>750</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1452,13 +1479,13 @@
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" s="3">
         <v>6</v>
@@ -1466,7 +1493,9 @@
       <c r="H10" s="3">
         <v>6</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="3">
+        <v>840</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1483,13 +1512,13 @@
         <v>2</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G11" s="3">
         <v>7</v>
@@ -1497,7 +1526,9 @@
       <c r="H11" s="3">
         <v>7</v>
       </c>
-      <c r="I11" s="3"/>
+      <c r="I11" s="3">
+        <v>900</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>

--- a/excel/map.xlsx
+++ b/excel/map.xlsx
@@ -40,6 +40,28 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+代表地图的id</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
@@ -69,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>编号</t>
   </si>
@@ -150,42 +172,6 @@
   </si>
   <si>
     <t>[3,100005]</t>
-  </si>
-  <si>
-    <t>航天基地</t>
-  </si>
-  <si>
-    <t>[200019,200014,200011]</t>
-  </si>
-  <si>
-    <t>[4,100006]</t>
-  </si>
-  <si>
-    <t>[200020,200014,200011]</t>
-  </si>
-  <si>
-    <t>[5,100005]</t>
-  </si>
-  <si>
-    <t>[200015,200014,200011]</t>
-  </si>
-  <si>
-    <t>[6,100004]</t>
-  </si>
-  <si>
-    <t>监狱</t>
-  </si>
-  <si>
-    <t>[200023,200014,200011]</t>
-  </si>
-  <si>
-    <t>[7,100005]</t>
-  </si>
-  <si>
-    <t>[200016,200015,200011]</t>
-  </si>
-  <si>
-    <t>[8,100006]</t>
   </si>
 </sst>
 </file>
@@ -1370,165 +1356,75 @@
       <c r="M6" s="3"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:13">
-      <c r="A7" s="3">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="3">
-        <v>3</v>
-      </c>
-      <c r="H7" s="3">
-        <v>6</v>
-      </c>
-      <c r="I7" s="3">
-        <v>720</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:13">
-      <c r="A8" s="3">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
-        <v>6</v>
-      </c>
-      <c r="I8" s="3">
-        <v>720</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:13">
-      <c r="A9" s="3">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="3">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3">
-        <v>7</v>
-      </c>
-      <c r="I9" s="3">
-        <v>750</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:13">
-      <c r="A10" s="3">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3">
-        <v>2</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="3">
-        <v>6</v>
-      </c>
-      <c r="H10" s="3">
-        <v>6</v>
-      </c>
-      <c r="I10" s="3">
-        <v>840</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:13">
-      <c r="A11" s="3">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3">
-        <v>2</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="3">
-        <v>7</v>
-      </c>
-      <c r="H11" s="3">
-        <v>7</v>
-      </c>
-      <c r="I11" s="3">
-        <v>900</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>

--- a/excel/map.xlsx
+++ b/excel/map.xlsx
@@ -1342,7 +1342,7 @@
         <v>26</v>
       </c>
       <c r="G6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>

--- a/excel/map.xlsx
+++ b/excel/map.xlsx
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>编号</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>游戏时长</t>
+  </si>
+  <si>
+    <t>ai等级列表</t>
   </si>
   <si>
     <t>id</t>
@@ -147,6 +150,9 @@
     <t>gameTime</t>
   </si>
   <si>
+    <t>agentList</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
   </si>
   <si>
     <t>[1,100003]</t>
+  </si>
+  <si>
+    <t>[0,1,2]</t>
   </si>
   <si>
     <t>[200018,200014,200011]</t>
@@ -1197,63 +1206,72 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:13">
@@ -1267,13 +1285,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -1284,7 +1302,9 @@
       <c r="I4" s="3">
         <v>600</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -1300,13 +1320,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -1317,7 +1337,9 @@
       <c r="I5" s="3">
         <v>600</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="J5" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -1333,13 +1355,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G6" s="3">
         <v>3</v>
@@ -1350,7 +1372,9 @@
       <c r="I6" s="3">
         <v>660</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
